--- a/ppt, excel, script/최종/01_3조_딱코_AI_드론 기반 보행자 검색추적을 위한 실시간 관제 시스템_1차프로젝트산출물/08_3조_딱코_AI_드론 기반 보행자 검색추적을 위한 실시간 관제 시스템_트러블슈팅.xlsx
+++ b/ppt, excel, script/최종/01_3조_딱코_AI_드론 기반 보행자 검색추적을 위한 실시간 관제 시스템_1차프로젝트산출물/08_3조_딱코_AI_드론 기반 보행자 검색추적을 위한 실시간 관제 시스템_트러블슈팅.xlsx
@@ -7,7 +7,7 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="트러블슈팅" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
   <si>
     <t>해소시각</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -161,12 +161,39 @@
     <t>메인 쓰레드에서 카메라로부터 프레임을 읽고 처리하는 동안 프레임 변조</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>확인자</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박정호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>박정호</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>parkjungho20@gamil.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인자 연락처</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>현재 트러블슈팅 문서는 기능적인 문제를 위주로 작성되어 있지만 현실에서 프로젝트를 진행할 때 발생하는 다양한 문제점들이 히스토리로 남아야 함.
+협업 툴 사용 중에 발생한 문제나 회의 중 의사소통이 부족해 발생한 생각의 엇갈림 등등 비기능적 문제를 포함해 다양한 사유로 발생한 거의 모든 문제들을 이곳에 기록해야 한다.
+트러블슈팅에서의 문제 발견과 해결 과정은 굉장히 중요한 부분이니 특히 신경쓰기(오히려 기능구현보다 중요도가 높다)
+트러블슈팅 잘 남기기 위해서는 그날 개발한 내용을 스크럼하여 기록하는 과정이 반드시 필요함.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -186,6 +213,14 @@
       <color theme="1" tint="0.14999847407452621"/>
       <name val="Consolas"/>
       <family val="3"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -211,10 +246,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -243,9 +279,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="14" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -523,165 +569,252 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B2:H8"/>
+  <dimension ref="B2:J13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="2.875" style="5" customWidth="1"/>
-    <col min="2" max="2" width="18.5" style="5" customWidth="1"/>
-    <col min="3" max="3" width="12.125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="20.25" style="5" customWidth="1"/>
-    <col min="5" max="5" width="67.75" style="5" customWidth="1"/>
-    <col min="6" max="6" width="21.5" style="5" customWidth="1"/>
-    <col min="7" max="7" width="56.625" style="5" customWidth="1"/>
-    <col min="8" max="8" width="49.875" style="5" customWidth="1"/>
-    <col min="9" max="16384" width="9" style="5"/>
+    <col min="2" max="3" width="18.5" style="5" customWidth="1"/>
+    <col min="4" max="4" width="24" style="5" customWidth="1"/>
+    <col min="5" max="5" width="12.125" style="5" customWidth="1"/>
+    <col min="6" max="6" width="20.25" style="5" customWidth="1"/>
+    <col min="7" max="7" width="67.75" style="5" customWidth="1"/>
+    <col min="8" max="8" width="21.5" style="5" customWidth="1"/>
+    <col min="9" max="9" width="56.625" style="5" customWidth="1"/>
+    <col min="10" max="10" width="49.875" style="5" customWidth="1"/>
+    <col min="11" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
         <v>46203</v>
       </c>
-      <c r="C3" s="2">
+      <c r="C3" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E3" s="2">
         <v>46203</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="5" t="s">
+      <c r="H3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="I3" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="6" t="s">
+      <c r="J3" s="6" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="2:8" ht="99" x14ac:dyDescent="0.3">
+    <row r="4" spans="2:10" ht="99" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>46205</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D4" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E4" s="2">
         <v>46205</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="F4" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="G4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="H4" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="I4" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="J4" s="4" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="5" spans="2:8" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="2:10" ht="75.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>46205</v>
       </c>
-      <c r="C5" s="2">
+      <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E5" s="2">
         <v>46205</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="G5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="H5" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="G5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="4" t="s">
+      <c r="J5" s="4" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="6" spans="2:8" ht="49.5" x14ac:dyDescent="0.3">
+    <row r="6" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>46211</v>
       </c>
-      <c r="C6" s="2">
+      <c r="C6" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E6" s="2">
         <v>46212</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="G6" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="H6" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="9" t="s">
+      <c r="I6" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="H6" s="4" t="s">
+      <c r="J6" s="4" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="2:8" ht="66" x14ac:dyDescent="0.3">
+    <row r="7" spans="2:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>46215</v>
       </c>
-      <c r="C7" s="2">
+      <c r="C7" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="E7" s="2">
         <v>46215</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="F7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="G7" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="H7" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G7" s="4" t="s">
+      <c r="I7" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="4" t="s">
+      <c r="J7" s="4" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="2:8" x14ac:dyDescent="0.3">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
       <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+    </row>
+    <row r="10" spans="2:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="12"/>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="12"/>
+      <c r="C11" s="12"/>
+      <c r="D11" s="12"/>
+      <c r="E11" s="12"/>
+      <c r="F11" s="12"/>
+      <c r="G11" s="12"/>
+      <c r="H11" s="12"/>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="12"/>
+      <c r="C12" s="12"/>
+      <c r="D12" s="12"/>
+      <c r="E12" s="12"/>
+      <c r="F12" s="12"/>
+      <c r="G12" s="12"/>
+      <c r="H12" s="12"/>
+    </row>
+    <row r="13" spans="2:10" ht="58.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="12"/>
+      <c r="C13" s="12"/>
+      <c r="D13" s="12"/>
+      <c r="E13" s="12"/>
+      <c r="F13" s="12"/>
+      <c r="G13" s="12"/>
+      <c r="H13" s="12"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B10:H13"/>
+  </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="D3" r:id="rId1"/>
+    <hyperlink ref="D4" r:id="rId2"/>
+    <hyperlink ref="D5" r:id="rId3"/>
+    <hyperlink ref="D6" r:id="rId4"/>
+    <hyperlink ref="D7" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967292" r:id="rId6"/>
 </worksheet>
 </file>